--- a/output/data_reports/latam_availability.xlsx
+++ b/output/data_reports/latam_availability.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="27">
   <si>
     <t>country</t>
   </si>
@@ -63,234 +63,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>has_tax</t>
   </si>
   <si>
@@ -306,403 +78,22 @@
     <t>2. Interpolation</t>
   </si>
   <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
     <t>3. Surveys, but no tax data</t>
   </si>
   <si>
     <t>1. Carry forward/backward</t>
   </si>
   <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
     <t>5. Tax and survey microdata</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>5. Tax and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>5. Tax and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>5. Tax and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>4. Tax tabulation and survey microdata</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>2. Interpolation</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>5. Tax and survey microdata</t>
-  </si>
-  <si>
-    <t>3. Surveys, but no tax data</t>
-  </si>
-  <si>
-    <t>1. Carry forward/backward</t>
   </si>
   <si>
     <t>admin_total</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>admin_wage</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>admin_other</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>no</t>
   </si>
 </sst>
 </file>
@@ -760,22 +151,22 @@
         <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s">
-        <v>190</v>
+        <v>24</v>
       </c>
       <c r="H1" t="s">
-        <v>218</v>
+        <v>25</v>
       </c>
       <c r="I1" t="s">
-        <v>225</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -795,16 +186,16 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -824,16 +215,16 @@
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -853,16 +244,16 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -882,16 +273,16 @@
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -911,16 +302,16 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -940,16 +331,16 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -969,16 +360,16 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -998,16 +389,16 @@
         <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -1027,16 +418,16 @@
         <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -1056,16 +447,16 @@
         <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -1085,16 +476,16 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -1114,16 +505,16 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -1143,16 +534,16 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I14" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1172,16 +563,16 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I15" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1201,16 +592,16 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1230,16 +621,16 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="I17" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1250,25 +641,25 @@
         <v>2016</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1279,25 +670,25 @@
         <v>2017</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1308,25 +699,25 @@
         <v>2018</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -1337,25 +728,25 @@
         <v>2019</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>226</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1366,7 +757,7 @@
         <v>2020</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1375,16 +766,16 @@
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1395,7 +786,7 @@
         <v>2021</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1404,16 +795,16 @@
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1424,7 +815,7 @@
         <v>2022</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1433,16 +824,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I24" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -1453,7 +844,7 @@
         <v>2023</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1462,16 +853,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1482,25 +873,25 @@
         <v>2024</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -1511,7 +902,7 @@
         <v>2000</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1520,16 +911,16 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>192</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1540,7 +931,7 @@
         <v>2001</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1549,16 +940,16 @@
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>193</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -1569,7 +960,7 @@
         <v>2002</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1578,16 +969,16 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>194</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1598,7 +989,7 @@
         <v>2003</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1607,16 +998,16 @@
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>195</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1627,7 +1018,7 @@
         <v>2004</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1636,16 +1027,16 @@
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>195</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1656,7 +1047,7 @@
         <v>2005</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1665,16 +1056,16 @@
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>195</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1685,7 +1076,7 @@
         <v>2006</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1694,16 +1085,16 @@
         <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="G33" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I33" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
@@ -1714,7 +1105,7 @@
         <v>2007</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1723,16 +1114,16 @@
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -1743,7 +1134,7 @@
         <v>2008</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1752,16 +1143,16 @@
         <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="G35" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
@@ -1772,7 +1163,7 @@
         <v>2009</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1781,16 +1172,16 @@
         <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I36" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1801,7 +1192,7 @@
         <v>2010</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1810,16 +1201,16 @@
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1830,7 +1221,7 @@
         <v>2011</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1839,16 +1230,16 @@
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G38" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I38" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1859,7 +1250,7 @@
         <v>2012</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1868,16 +1259,16 @@
         <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G39" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -1888,7 +1279,7 @@
         <v>2013</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1897,16 +1288,16 @@
         <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G40" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I40" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1917,7 +1308,7 @@
         <v>2014</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1926,16 +1317,16 @@
         <v>4</v>
       </c>
       <c r="F41" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
@@ -1946,7 +1337,7 @@
         <v>2015</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1955,16 +1346,16 @@
         <v>4</v>
       </c>
       <c r="F42" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I42" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -1975,7 +1366,7 @@
         <v>2016</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1984,16 +1375,16 @@
         <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -2004,7 +1395,7 @@
         <v>2017</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2013,16 +1404,16 @@
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G44" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -2033,7 +1424,7 @@
         <v>2018</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2042,16 +1433,16 @@
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G45" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -2062,7 +1453,7 @@
         <v>2019</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2071,16 +1462,16 @@
         <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G46" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -2091,7 +1482,7 @@
         <v>2020</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2100,16 +1491,16 @@
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -2120,7 +1511,7 @@
         <v>2021</v>
       </c>
       <c r="C48" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2129,16 +1520,16 @@
         <v>4</v>
       </c>
       <c r="F48" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I48" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -2149,7 +1540,7 @@
         <v>2022</v>
       </c>
       <c r="C49" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2158,16 +1549,16 @@
         <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -2178,7 +1569,7 @@
         <v>2023</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2187,16 +1578,16 @@
         <v>4</v>
       </c>
       <c r="F50" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="H50" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I50" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
@@ -2207,25 +1598,25 @@
         <v>2024</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>197</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I51" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -2236,7 +1627,7 @@
         <v>2000</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2245,16 +1636,16 @@
         <v>3</v>
       </c>
       <c r="F52" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="G52" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -2265,7 +1656,7 @@
         <v>2001</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2274,16 +1665,16 @@
         <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -2294,7 +1685,7 @@
         <v>2002</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2303,16 +1694,16 @@
         <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I54" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -2323,7 +1714,7 @@
         <v>2003</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2332,16 +1723,16 @@
         <v>3</v>
       </c>
       <c r="F55" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="G55" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I55" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -2352,7 +1743,7 @@
         <v>2004</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2361,16 +1752,16 @@
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>197</v>
+        <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I56" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -2381,7 +1772,7 @@
         <v>2005</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2390,16 +1781,16 @@
         <v>2</v>
       </c>
       <c r="F57" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H57" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I57" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -2410,7 +1801,7 @@
         <v>2006</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2419,16 +1810,16 @@
         <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I58" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -2439,7 +1830,7 @@
         <v>2007</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2448,16 +1839,16 @@
         <v>2</v>
       </c>
       <c r="F59" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I59" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -2468,7 +1859,7 @@
         <v>2008</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2477,16 +1868,16 @@
         <v>2</v>
       </c>
       <c r="F60" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H60" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -2497,7 +1888,7 @@
         <v>2009</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2506,16 +1897,16 @@
         <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -2526,7 +1917,7 @@
         <v>2010</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2535,16 +1926,16 @@
         <v>2</v>
       </c>
       <c r="F62" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H62" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -2555,7 +1946,7 @@
         <v>2011</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2564,16 +1955,16 @@
         <v>4</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -2584,25 +1975,25 @@
         <v>2012</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -2613,7 +2004,7 @@
         <v>2013</v>
       </c>
       <c r="C65" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2622,16 +2013,16 @@
         <v>4</v>
       </c>
       <c r="F65" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H65" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
@@ -2642,7 +2033,7 @@
         <v>2014</v>
       </c>
       <c r="C66" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2651,16 +2042,16 @@
         <v>2</v>
       </c>
       <c r="F66" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H66" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
@@ -2671,7 +2062,7 @@
         <v>2015</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2680,16 +2071,16 @@
         <v>4</v>
       </c>
       <c r="F67" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="G67" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H67" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -2700,7 +2091,7 @@
         <v>2016</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2709,16 +2100,16 @@
         <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I68" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -2729,7 +2120,7 @@
         <v>2017</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2738,16 +2129,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="G69" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H69" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I69" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -2758,7 +2149,7 @@
         <v>2018</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2767,16 +2158,16 @@
         <v>2</v>
       </c>
       <c r="F70" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="G70" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H70" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I70" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
@@ -2787,7 +2178,7 @@
         <v>2019</v>
       </c>
       <c r="C71" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2796,16 +2187,16 @@
         <v>2</v>
       </c>
       <c r="F71" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="G71" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H71" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I71" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
@@ -2816,7 +2207,7 @@
         <v>2020</v>
       </c>
       <c r="C72" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2825,16 +2216,16 @@
         <v>4</v>
       </c>
       <c r="F72" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="G72" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H72" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I72" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73">
@@ -2845,7 +2236,7 @@
         <v>2021</v>
       </c>
       <c r="C73" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2854,16 +2245,16 @@
         <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H73" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I73" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
@@ -2874,7 +2265,7 @@
         <v>2022</v>
       </c>
       <c r="C74" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2883,16 +2274,16 @@
         <v>4</v>
       </c>
       <c r="F74" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="G74" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H74" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I74" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
@@ -2903,25 +2294,25 @@
         <v>2023</v>
       </c>
       <c r="C75" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D75">
         <v>1</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>198</v>
+        <v>14</v>
       </c>
       <c r="H75" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I75" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76">
@@ -2932,25 +2323,25 @@
         <v>2024</v>
       </c>
       <c r="C76" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="G76" t="s">
-        <v>199</v>
+        <v>14</v>
       </c>
       <c r="H76" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I76" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -2961,7 +2352,7 @@
         <v>2000</v>
       </c>
       <c r="C77" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2970,16 +2361,16 @@
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="G77" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I77" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -2990,7 +2381,7 @@
         <v>2001</v>
       </c>
       <c r="C78" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -2999,16 +2390,16 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="G78" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H78" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I78" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
@@ -3019,7 +2410,7 @@
         <v>2002</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3028,16 +2419,16 @@
         <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="G79" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I79" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
@@ -3048,7 +2439,7 @@
         <v>2003</v>
       </c>
       <c r="C80" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3057,16 +2448,16 @@
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="G80" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I80" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81">
@@ -3077,7 +2468,7 @@
         <v>2004</v>
       </c>
       <c r="C81" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3086,16 +2477,16 @@
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I81" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82">
@@ -3106,7 +2497,7 @@
         <v>2005</v>
       </c>
       <c r="C82" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3115,16 +2506,16 @@
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I82" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
@@ -3135,7 +2526,7 @@
         <v>2006</v>
       </c>
       <c r="C83" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3144,16 +2535,16 @@
         <v>2</v>
       </c>
       <c r="F83" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I83" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84">
@@ -3164,7 +2555,7 @@
         <v>2007</v>
       </c>
       <c r="C84" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3173,16 +2564,16 @@
         <v>2</v>
       </c>
       <c r="F84" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I84" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
@@ -3193,7 +2584,7 @@
         <v>2008</v>
       </c>
       <c r="C85" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3202,16 +2593,16 @@
         <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="G85" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I85" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -3222,7 +2613,7 @@
         <v>2009</v>
       </c>
       <c r="C86" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3231,16 +2622,16 @@
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="G86" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I86" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
@@ -3251,7 +2642,7 @@
         <v>2010</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3260,16 +2651,16 @@
         <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="G87" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I87" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
@@ -3280,7 +2671,7 @@
         <v>2011</v>
       </c>
       <c r="C88" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3289,16 +2680,16 @@
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="G88" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I88" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89">
@@ -3309,7 +2700,7 @@
         <v>2012</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3318,16 +2709,16 @@
         <v>3</v>
       </c>
       <c r="F89" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="G89" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I89" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90">
@@ -3338,7 +2729,7 @@
         <v>2013</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3347,16 +2738,16 @@
         <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="G90" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="H90" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I90" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91">
@@ -3367,7 +2758,7 @@
         <v>2014</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3376,16 +2767,16 @@
         <v>4</v>
       </c>
       <c r="F91" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G91" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H91" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I91" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -3396,7 +2787,7 @@
         <v>2015</v>
       </c>
       <c r="C92" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3405,16 +2796,16 @@
         <v>4</v>
       </c>
       <c r="F92" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G92" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H92" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I92" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -3425,7 +2816,7 @@
         <v>2016</v>
       </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3434,16 +2825,16 @@
         <v>4</v>
       </c>
       <c r="F93" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G93" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H93" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I93" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
@@ -3454,7 +2845,7 @@
         <v>2017</v>
       </c>
       <c r="C94" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3463,16 +2854,16 @@
         <v>4</v>
       </c>
       <c r="F94" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H94" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I94" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -3483,7 +2874,7 @@
         <v>2018</v>
       </c>
       <c r="C95" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3492,16 +2883,16 @@
         <v>4</v>
       </c>
       <c r="F95" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H95" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I95" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -3512,7 +2903,7 @@
         <v>2019</v>
       </c>
       <c r="C96" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3521,16 +2912,16 @@
         <v>4</v>
       </c>
       <c r="F96" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G96" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H96" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I96" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -3541,7 +2932,7 @@
         <v>2020</v>
       </c>
       <c r="C97" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3550,16 +2941,16 @@
         <v>4</v>
       </c>
       <c r="F97" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H97" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I97" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -3570,7 +2961,7 @@
         <v>2021</v>
       </c>
       <c r="C98" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3579,16 +2970,16 @@
         <v>4</v>
       </c>
       <c r="F98" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H98" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I98" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -3599,7 +2990,7 @@
         <v>2022</v>
       </c>
       <c r="C99" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3608,16 +2999,16 @@
         <v>4</v>
       </c>
       <c r="F99" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G99" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H99" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I99" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
@@ -3628,7 +3019,7 @@
         <v>2023</v>
       </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3637,16 +3028,16 @@
         <v>4</v>
       </c>
       <c r="F100" t="s">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="H100" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I100" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101">
@@ -3657,25 +3048,25 @@
         <v>2024</v>
       </c>
       <c r="C101" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="G101" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H101" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I101" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102">
@@ -3686,7 +3077,7 @@
         <v>2000</v>
       </c>
       <c r="C102" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3695,16 +3086,16 @@
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="G102" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H102" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="I102" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103">
@@ -3715,7 +3106,7 @@
         <v>2001</v>
       </c>
       <c r="C103" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3724,16 +3115,16 @@
         <v>5</v>
       </c>
       <c r="F103" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G103" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I103" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
@@ -3744,7 +3135,7 @@
         <v>2002</v>
       </c>
       <c r="C104" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3753,16 +3144,16 @@
         <v>5</v>
       </c>
       <c r="F104" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G104" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I104" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105">
@@ -3773,7 +3164,7 @@
         <v>2003</v>
       </c>
       <c r="C105" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3782,16 +3173,16 @@
         <v>5</v>
       </c>
       <c r="F105" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G105" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I105" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106">
@@ -3802,7 +3193,7 @@
         <v>2004</v>
       </c>
       <c r="C106" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3811,16 +3202,16 @@
         <v>5</v>
       </c>
       <c r="F106" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G106" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I106" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107">
@@ -3831,7 +3222,7 @@
         <v>2005</v>
       </c>
       <c r="C107" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3840,16 +3231,16 @@
         <v>5</v>
       </c>
       <c r="F107" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G107" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I107" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
@@ -3860,7 +3251,7 @@
         <v>2006</v>
       </c>
       <c r="C108" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -3869,16 +3260,16 @@
         <v>5</v>
       </c>
       <c r="F108" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G108" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I108" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109">
@@ -3889,7 +3280,7 @@
         <v>2007</v>
       </c>
       <c r="C109" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3898,16 +3289,16 @@
         <v>5</v>
       </c>
       <c r="F109" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G109" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I109" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110">
@@ -3918,7 +3309,7 @@
         <v>2008</v>
       </c>
       <c r="C110" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -3927,16 +3318,16 @@
         <v>5</v>
       </c>
       <c r="F110" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G110" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I110" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111">
@@ -3947,7 +3338,7 @@
         <v>2009</v>
       </c>
       <c r="C111" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3956,16 +3347,16 @@
         <v>5</v>
       </c>
       <c r="F111" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G111" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H111" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I111" t="s">
-        <v>227</v>
+        <v>15</v>
       </c>
     </row>
     <row r="112">
@@ -3976,7 +3367,7 @@
         <v>2010</v>
       </c>
       <c r="C112" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3985,16 +3376,16 @@
         <v>5</v>
       </c>
       <c r="F112" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G112" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H112" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I112" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113">
@@ -4005,7 +3396,7 @@
         <v>2011</v>
       </c>
       <c r="C113" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4014,16 +3405,16 @@
         <v>5</v>
       </c>
       <c r="F113" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G113" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I113" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114">
@@ -4034,7 +3425,7 @@
         <v>2012</v>
       </c>
       <c r="C114" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -4043,16 +3434,16 @@
         <v>5</v>
       </c>
       <c r="F114" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G114" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H114" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I114" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115">
@@ -4063,7 +3454,7 @@
         <v>2013</v>
       </c>
       <c r="C115" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -4072,16 +3463,16 @@
         <v>5</v>
       </c>
       <c r="F115" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G115" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I115" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116">
@@ -4092,7 +3483,7 @@
         <v>2014</v>
       </c>
       <c r="C116" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4101,16 +3492,16 @@
         <v>5</v>
       </c>
       <c r="F116" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G116" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I116" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117">
@@ -4121,7 +3512,7 @@
         <v>2015</v>
       </c>
       <c r="C117" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4130,16 +3521,16 @@
         <v>5</v>
       </c>
       <c r="F117" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G117" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I117" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118">
@@ -4150,7 +3541,7 @@
         <v>2016</v>
       </c>
       <c r="C118" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4159,16 +3550,16 @@
         <v>5</v>
       </c>
       <c r="F118" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="G118" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="I118" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119">
@@ -4179,7 +3570,7 @@
         <v>2017</v>
       </c>
       <c r="C119" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4188,16 +3579,16 @@
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="G119" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I119" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120">
@@ -4208,7 +3599,7 @@
         <v>2018</v>
       </c>
       <c r="C120" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4217,16 +3608,16 @@
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="G120" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I120" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121">
@@ -4237,7 +3628,7 @@
         <v>2019</v>
       </c>
       <c r="C121" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4246,16 +3637,16 @@
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="G121" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I121" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122">
@@ -4266,7 +3657,7 @@
         <v>2020</v>
       </c>
       <c r="C122" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4275,16 +3666,16 @@
         <v>3</v>
       </c>
       <c r="F122" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="G122" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I122" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123">
@@ -4295,7 +3686,7 @@
         <v>2021</v>
       </c>
       <c r="C123" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -4304,16 +3695,16 @@
         <v>3</v>
       </c>
       <c r="F123" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="G123" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H123" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I123" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124">
@@ -4324,7 +3715,7 @@
         <v>2022</v>
       </c>
       <c r="C124" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -4333,16 +3724,16 @@
         <v>3</v>
       </c>
       <c r="F124" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="G124" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I124" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125">
@@ -4353,7 +3744,7 @@
         <v>2023</v>
       </c>
       <c r="C125" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -4362,16 +3753,16 @@
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="G125" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H125" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I125" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126">
@@ -4382,25 +3773,25 @@
         <v>2024</v>
       </c>
       <c r="C126" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="G126" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I126" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127">
@@ -4411,7 +3802,7 @@
         <v>2000</v>
       </c>
       <c r="C127" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -4420,16 +3811,16 @@
         <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G127" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H127" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I127" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128">
@@ -4440,7 +3831,7 @@
         <v>2001</v>
       </c>
       <c r="C128" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -4449,16 +3840,16 @@
         <v>3</v>
       </c>
       <c r="F128" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G128" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H128" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I128" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129">
@@ -4469,7 +3860,7 @@
         <v>2002</v>
       </c>
       <c r="C129" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -4478,16 +3869,16 @@
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G129" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H129" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I129" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130">
@@ -4498,7 +3889,7 @@
         <v>2003</v>
       </c>
       <c r="C130" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -4507,16 +3898,16 @@
         <v>3</v>
       </c>
       <c r="F130" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G130" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H130" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I130" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131">
@@ -4527,7 +3918,7 @@
         <v>2004</v>
       </c>
       <c r="C131" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -4536,16 +3927,16 @@
         <v>3</v>
       </c>
       <c r="F131" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G131" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H131" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I131" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132">
@@ -4556,7 +3947,7 @@
         <v>2005</v>
       </c>
       <c r="C132" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -4565,16 +3956,16 @@
         <v>3</v>
       </c>
       <c r="F132" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G132" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I132" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133">
@@ -4585,7 +3976,7 @@
         <v>2006</v>
       </c>
       <c r="C133" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -4594,16 +3985,16 @@
         <v>3</v>
       </c>
       <c r="F133" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G133" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I133" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134">
@@ -4614,7 +4005,7 @@
         <v>2007</v>
       </c>
       <c r="C134" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -4623,16 +4014,16 @@
         <v>3</v>
       </c>
       <c r="F134" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G134" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H134" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I134" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135">
@@ -4643,7 +4034,7 @@
         <v>2008</v>
       </c>
       <c r="C135" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -4652,16 +4043,16 @@
         <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G135" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H135" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I135" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136">
@@ -4672,7 +4063,7 @@
         <v>2009</v>
       </c>
       <c r="C136" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -4681,16 +4072,16 @@
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G136" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H136" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I136" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
@@ -4701,7 +4092,7 @@
         <v>2010</v>
       </c>
       <c r="C137" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -4710,16 +4101,16 @@
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G137" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H137" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I137" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="138">
@@ -4730,7 +4121,7 @@
         <v>2011</v>
       </c>
       <c r="C138" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -4739,16 +4130,16 @@
         <v>3</v>
       </c>
       <c r="F138" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="G138" t="s">
-        <v>201</v>
+        <v>15</v>
       </c>
       <c r="H138" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I138" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139">
@@ -4759,7 +4150,7 @@
         <v>2012</v>
       </c>
       <c r="C139" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4768,16 +4159,16 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G139" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H139" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I139" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140">
@@ -4788,7 +4179,7 @@
         <v>2013</v>
       </c>
       <c r="C140" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4797,16 +4188,16 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G140" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H140" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I140" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141">
@@ -4817,7 +4208,7 @@
         <v>2014</v>
       </c>
       <c r="C141" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4826,16 +4217,16 @@
         <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G141" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H141" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I141" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142">
@@ -4846,7 +4237,7 @@
         <v>2015</v>
       </c>
       <c r="C142" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4855,16 +4246,16 @@
         <v>4</v>
       </c>
       <c r="F142" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G142" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H142" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I142" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143">
@@ -4875,7 +4266,7 @@
         <v>2016</v>
       </c>
       <c r="C143" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -4884,16 +4275,16 @@
         <v>4</v>
       </c>
       <c r="F143" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G143" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H143" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I143" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144">
@@ -4904,7 +4295,7 @@
         <v>2017</v>
       </c>
       <c r="C144" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -4913,16 +4304,16 @@
         <v>4</v>
       </c>
       <c r="F144" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G144" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H144" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I144" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="145">
@@ -4933,7 +4324,7 @@
         <v>2018</v>
       </c>
       <c r="C145" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4942,16 +4333,16 @@
         <v>4</v>
       </c>
       <c r="F145" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G145" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H145" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I145" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146">
@@ -4962,7 +4353,7 @@
         <v>2019</v>
       </c>
       <c r="C146" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -4971,16 +4362,16 @@
         <v>4</v>
       </c>
       <c r="F146" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G146" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H146" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I146" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147">
@@ -4991,7 +4382,7 @@
         <v>2020</v>
       </c>
       <c r="C147" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -5000,16 +4391,16 @@
         <v>4</v>
       </c>
       <c r="F147" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="G147" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="H147" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I147" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
@@ -5020,7 +4411,7 @@
         <v>2021</v>
       </c>
       <c r="C148" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -5029,16 +4420,16 @@
         <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="G148" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H148" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I148" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149">
@@ -5049,7 +4440,7 @@
         <v>2022</v>
       </c>
       <c r="C149" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -5058,16 +4449,16 @@
         <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="G149" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I149" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150">
@@ -5078,7 +4469,7 @@
         <v>2023</v>
       </c>
       <c r="C150" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -5087,16 +4478,16 @@
         <v>3</v>
       </c>
       <c r="F150" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="G150" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H150" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I150" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151">
@@ -5107,25 +4498,25 @@
         <v>2024</v>
       </c>
       <c r="C151" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F151" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="G151" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H151" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I151" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152">
@@ -5136,7 +4527,7 @@
         <v>2000</v>
       </c>
       <c r="C152" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -5145,16 +4536,16 @@
         <v>1</v>
       </c>
       <c r="F152" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="G152" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H152" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I152" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153">
@@ -5165,7 +4556,7 @@
         <v>2001</v>
       </c>
       <c r="C153" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -5174,16 +4565,16 @@
         <v>3</v>
       </c>
       <c r="F153" t="s">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="G153" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H153" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I153" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154">
@@ -5194,7 +4585,7 @@
         <v>2002</v>
       </c>
       <c r="C154" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -5203,16 +4594,16 @@
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="G154" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H154" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I154" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155">
@@ -5223,7 +4614,7 @@
         <v>2003</v>
       </c>
       <c r="C155" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -5232,16 +4623,16 @@
         <v>3</v>
       </c>
       <c r="F155" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="G155" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H155" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I155" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156">
@@ -5252,7 +4643,7 @@
         <v>2004</v>
       </c>
       <c r="C156" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -5261,16 +4652,16 @@
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>143</v>
+        <v>20</v>
       </c>
       <c r="G156" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H156" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I156" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157">
@@ -5281,7 +4672,7 @@
         <v>2005</v>
       </c>
       <c r="C157" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -5290,16 +4681,16 @@
         <v>3</v>
       </c>
       <c r="F157" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="G157" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H157" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I157" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158">
@@ -5310,7 +4701,7 @@
         <v>2006</v>
       </c>
       <c r="C158" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -5319,16 +4710,16 @@
         <v>3</v>
       </c>
       <c r="F158" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="G158" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H158" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I158" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159">
@@ -5339,7 +4730,7 @@
         <v>2007</v>
       </c>
       <c r="C159" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -5348,16 +4739,16 @@
         <v>3</v>
       </c>
       <c r="F159" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="G159" t="s">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="H159" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I159" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="160">
@@ -5368,25 +4759,25 @@
         <v>2008</v>
       </c>
       <c r="C160" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F160" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="G160" t="s">
-        <v>204</v>
+        <v>15</v>
       </c>
       <c r="H160" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I160" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161">
@@ -5397,25 +4788,25 @@
         <v>2009</v>
       </c>
       <c r="C161" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F161" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="G161" t="s">
-        <v>204</v>
+        <v>15</v>
       </c>
       <c r="H161" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I161" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162">
@@ -5426,25 +4817,25 @@
         <v>2010</v>
       </c>
       <c r="C162" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F162" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="G162" t="s">
-        <v>204</v>
+        <v>15</v>
       </c>
       <c r="H162" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I162" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163">
@@ -5455,25 +4846,25 @@
         <v>2011</v>
       </c>
       <c r="C163" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F163" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="G163" t="s">
-        <v>204</v>
+        <v>15</v>
       </c>
       <c r="H163" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I163" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164">
@@ -5484,7 +4875,7 @@
         <v>2012</v>
       </c>
       <c r="C164" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -5493,16 +4884,16 @@
         <v>3</v>
       </c>
       <c r="F164" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G164" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H164" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I164" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="165">
@@ -5513,7 +4904,7 @@
         <v>2013</v>
       </c>
       <c r="C165" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -5522,16 +4913,16 @@
         <v>3</v>
       </c>
       <c r="F165" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G165" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H165" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I165" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="166">
@@ -5542,7 +4933,7 @@
         <v>2014</v>
       </c>
       <c r="C166" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -5551,16 +4942,16 @@
         <v>3</v>
       </c>
       <c r="F166" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G166" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H166" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I166" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="167">
@@ -5571,7 +4962,7 @@
         <v>2015</v>
       </c>
       <c r="C167" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -5580,16 +4971,16 @@
         <v>3</v>
       </c>
       <c r="F167" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G167" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H167" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I167" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="168">
@@ -5600,7 +4991,7 @@
         <v>2016</v>
       </c>
       <c r="C168" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -5609,16 +5000,16 @@
         <v>3</v>
       </c>
       <c r="F168" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G168" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H168" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I168" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169">
@@ -5629,7 +5020,7 @@
         <v>2017</v>
       </c>
       <c r="C169" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -5638,16 +5029,16 @@
         <v>3</v>
       </c>
       <c r="F169" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G169" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H169" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I169" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170">
@@ -5658,7 +5049,7 @@
         <v>2018</v>
       </c>
       <c r="C170" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -5667,16 +5058,16 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G170" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H170" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I170" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171">
@@ -5687,7 +5078,7 @@
         <v>2019</v>
       </c>
       <c r="C171" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -5696,16 +5087,16 @@
         <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G171" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H171" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I171" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172">
@@ -5716,7 +5107,7 @@
         <v>2020</v>
       </c>
       <c r="C172" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -5725,16 +5116,16 @@
         <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G172" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H172" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I172" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173">
@@ -5745,7 +5136,7 @@
         <v>2021</v>
       </c>
       <c r="C173" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -5754,16 +5145,16 @@
         <v>3</v>
       </c>
       <c r="F173" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G173" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H173" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I173" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174">
@@ -5774,7 +5165,7 @@
         <v>2022</v>
       </c>
       <c r="C174" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -5783,16 +5174,16 @@
         <v>3</v>
       </c>
       <c r="F174" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G174" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H174" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I174" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175">
@@ -5803,7 +5194,7 @@
         <v>2023</v>
       </c>
       <c r="C175" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -5812,16 +5203,16 @@
         <v>3</v>
       </c>
       <c r="F175" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="G175" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H175" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I175" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176">
@@ -5832,25 +5223,25 @@
         <v>2024</v>
       </c>
       <c r="C176" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D176">
         <v>0</v>
       </c>
       <c r="E176">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F176" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="G176" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H176" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I176" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177">
@@ -5861,7 +5252,7 @@
         <v>2000</v>
       </c>
       <c r="C177" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -5870,16 +5261,16 @@
         <v>3</v>
       </c>
       <c r="F177" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="G177" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H177" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I177" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178">
@@ -5890,7 +5281,7 @@
         <v>2001</v>
       </c>
       <c r="C178" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -5899,16 +5290,16 @@
         <v>2</v>
       </c>
       <c r="F178" t="s">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="G178" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H178" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I178" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179">
@@ -5919,7 +5310,7 @@
         <v>2002</v>
       </c>
       <c r="C179" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -5928,16 +5319,16 @@
         <v>3</v>
       </c>
       <c r="F179" t="s">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="G179" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H179" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I179" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180">
@@ -5948,7 +5339,7 @@
         <v>2003</v>
       </c>
       <c r="C180" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -5957,16 +5348,16 @@
         <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="G180" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H180" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I180" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181">
@@ -5977,7 +5368,7 @@
         <v>2004</v>
       </c>
       <c r="C181" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -5986,16 +5377,16 @@
         <v>3</v>
       </c>
       <c r="F181" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="G181" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H181" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I181" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182">
@@ -6006,7 +5397,7 @@
         <v>2005</v>
       </c>
       <c r="C182" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -6015,16 +5406,16 @@
         <v>2</v>
       </c>
       <c r="F182" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="G182" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H182" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I182" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183">
@@ -6035,7 +5426,7 @@
         <v>2006</v>
       </c>
       <c r="C183" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -6044,16 +5435,16 @@
         <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="G183" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H183" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I183" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184">
@@ -6064,7 +5455,7 @@
         <v>2007</v>
       </c>
       <c r="C184" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -6073,16 +5464,16 @@
         <v>2</v>
       </c>
       <c r="F184" t="s">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="G184" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H184" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I184" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185">
@@ -6093,7 +5484,7 @@
         <v>2008</v>
       </c>
       <c r="C185" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="D185">
         <v>0</v>
@@ -6102,16 +5493,16 @@
         <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="G185" t="s">
-        <v>205</v>
+        <v>15</v>
       </c>
       <c r="H185" t="s">
-        <v>222</v>
+        <v>15</v>
       </c>
       <c r="I185" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="186">
@@ -6122,7 +5513,7 @@
         <v>2009</v>
       </c>
       <c r="C186" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -6131,16 +5522,16 @@
         <v>2</v>
       </c>
       <c r="F186" t="s">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="G186" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="H186" t="s">
-        <v>223</v>
+        <v>15</v>
       </c>
       <c r="I186" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="187">
@@ -6151,7 +5542,7 @@
         <v>2010</v>
       </c>
       <c r="C187" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -6160,16 +5551,16 @@
         <v>5</v>
       </c>
       <c r="F187" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="G187" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="H187" t="s">
-        <v>223</v>
+        <v>15</v>
       </c>
       <c r="I187" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188">
@@ -6180,7 +5571,7 @@
         <v>2011</v>
       </c>
       <c r="C188" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -6189,16 +5580,16 @@
         <v>2</v>
       </c>
       <c r="F188" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="G188" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="H188" t="s">
-        <v>223</v>
+        <v>15</v>
       </c>
       <c r="I188" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189">
@@ -6209,7 +5600,7 @@
         <v>2012</v>
       </c>
       <c r="C189" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -6218,16 +5609,16 @@
         <v>5</v>
       </c>
       <c r="F189" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="G189" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="H189" t="s">
-        <v>223</v>
+        <v>15</v>
       </c>
       <c r="I189" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190">
@@ -6238,7 +5629,7 @@
         <v>2013</v>
       </c>
       <c r="C190" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -6247,16 +5638,16 @@
         <v>2</v>
       </c>
       <c r="F190" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="G190" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="H190" t="s">
-        <v>223</v>
+        <v>15</v>
       </c>
       <c r="I190" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="191">
@@ -6267,7 +5658,7 @@
         <v>2014</v>
       </c>
       <c r="C191" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -6276,16 +5667,16 @@
         <v>5</v>
       </c>
       <c r="F191" t="s">
-        <v>162</v>
+        <v>23</v>
       </c>
       <c r="G191" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="H191" t="s">
-        <v>223</v>
+        <v>15</v>
       </c>
       <c r="I191" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192">
@@ -6296,7 +5687,7 @@
         <v>2015</v>
       </c>
       <c r="C192" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -6305,16 +5696,16 @@
         <v>2</v>
       </c>
       <c r="F192" t="s">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="G192" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H192" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I192" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193">
@@ -6325,7 +5716,7 @@
         <v>2016</v>
       </c>
       <c r="C193" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -6334,16 +5725,16 @@
         <v>3</v>
       </c>
       <c r="F193" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="G193" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H193" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I193" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194">
@@ -6354,7 +5745,7 @@
         <v>2017</v>
       </c>
       <c r="C194" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -6363,16 +5754,16 @@
         <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="G194" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H194" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I194" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195">
@@ -6383,7 +5774,7 @@
         <v>2018</v>
       </c>
       <c r="C195" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -6392,16 +5783,16 @@
         <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="G195" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H195" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I195" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="196">
@@ -6412,7 +5803,7 @@
         <v>2019</v>
       </c>
       <c r="C196" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="D196">
         <v>0</v>
@@ -6421,16 +5812,16 @@
         <v>2</v>
       </c>
       <c r="F196" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="G196" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H196" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I196" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="197">
@@ -6441,7 +5832,7 @@
         <v>2020</v>
       </c>
       <c r="C197" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="D197">
         <v>0</v>
@@ -6450,16 +5841,16 @@
         <v>3</v>
       </c>
       <c r="F197" t="s">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="G197" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H197" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I197" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198">
@@ -6470,7 +5861,7 @@
         <v>2021</v>
       </c>
       <c r="C198" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -6479,16 +5870,16 @@
         <v>2</v>
       </c>
       <c r="F198" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="G198" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H198" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I198" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="199">
@@ -6499,7 +5890,7 @@
         <v>2022</v>
       </c>
       <c r="C199" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -6508,16 +5899,16 @@
         <v>3</v>
       </c>
       <c r="F199" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="G199" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H199" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I199" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200">
@@ -6528,25 +5919,25 @@
         <v>2023</v>
       </c>
       <c r="C200" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="D200">
         <v>0</v>
       </c>
       <c r="E200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F200" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="G200" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H200" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I200" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="201">
@@ -6557,25 +5948,25 @@
         <v>2024</v>
       </c>
       <c r="C201" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D201">
         <v>0</v>
       </c>
       <c r="E201">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F201" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="G201" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H201" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I201" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="202">
@@ -6586,7 +5977,7 @@
         <v>2000</v>
       </c>
       <c r="C202" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D202">
         <v>0</v>
@@ -6595,16 +5986,16 @@
         <v>3</v>
       </c>
       <c r="F202" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G202" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H202" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I202" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203">
@@ -6615,7 +6006,7 @@
         <v>2001</v>
       </c>
       <c r="C203" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -6624,16 +6015,16 @@
         <v>3</v>
       </c>
       <c r="F203" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G203" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H203" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I203" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="204">
@@ -6644,7 +6035,7 @@
         <v>2002</v>
       </c>
       <c r="C204" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -6653,16 +6044,16 @@
         <v>3</v>
       </c>
       <c r="F204" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G204" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H204" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I204" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205">
@@ -6673,7 +6064,7 @@
         <v>2003</v>
       </c>
       <c r="C205" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -6682,16 +6073,16 @@
         <v>3</v>
       </c>
       <c r="F205" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G205" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H205" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I205" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="206">
@@ -6702,7 +6093,7 @@
         <v>2004</v>
       </c>
       <c r="C206" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -6711,16 +6102,16 @@
         <v>3</v>
       </c>
       <c r="F206" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G206" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H206" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I206" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="207">
@@ -6731,7 +6122,7 @@
         <v>2005</v>
       </c>
       <c r="C207" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -6740,16 +6131,16 @@
         <v>3</v>
       </c>
       <c r="F207" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G207" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H207" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I207" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="208">
@@ -6760,7 +6151,7 @@
         <v>2006</v>
       </c>
       <c r="C208" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -6769,16 +6160,16 @@
         <v>3</v>
       </c>
       <c r="F208" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G208" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H208" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I208" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209">
@@ -6789,7 +6180,7 @@
         <v>2007</v>
       </c>
       <c r="C209" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D209">
         <v>0</v>
@@ -6798,16 +6189,16 @@
         <v>3</v>
       </c>
       <c r="F209" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G209" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H209" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I209" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="210">
@@ -6818,7 +6209,7 @@
         <v>2008</v>
       </c>
       <c r="C210" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -6827,16 +6218,16 @@
         <v>3</v>
       </c>
       <c r="F210" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G210" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H210" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I210" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="211">
@@ -6847,7 +6238,7 @@
         <v>2009</v>
       </c>
       <c r="C211" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D211">
         <v>0</v>
@@ -6856,16 +6247,16 @@
         <v>3</v>
       </c>
       <c r="F211" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G211" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H211" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I211" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212">
@@ -6876,7 +6267,7 @@
         <v>2010</v>
       </c>
       <c r="C212" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D212">
         <v>0</v>
@@ -6885,16 +6276,16 @@
         <v>3</v>
       </c>
       <c r="F212" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G212" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H212" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I212" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="213">
@@ -6905,7 +6296,7 @@
         <v>2011</v>
       </c>
       <c r="C213" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D213">
         <v>0</v>
@@ -6914,16 +6305,16 @@
         <v>3</v>
       </c>
       <c r="F213" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G213" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H213" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I213" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214">
@@ -6934,7 +6325,7 @@
         <v>2012</v>
       </c>
       <c r="C214" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D214">
         <v>0</v>
@@ -6943,16 +6334,16 @@
         <v>3</v>
       </c>
       <c r="F214" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G214" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H214" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I214" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="215">
@@ -6963,7 +6354,7 @@
         <v>2013</v>
       </c>
       <c r="C215" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D215">
         <v>0</v>
@@ -6972,16 +6363,16 @@
         <v>3</v>
       </c>
       <c r="F215" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G215" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H215" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I215" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="216">
@@ -6992,7 +6383,7 @@
         <v>2014</v>
       </c>
       <c r="C216" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D216">
         <v>0</v>
@@ -7001,16 +6392,16 @@
         <v>3</v>
       </c>
       <c r="F216" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G216" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H216" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I216" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="217">
@@ -7021,7 +6412,7 @@
         <v>2015</v>
       </c>
       <c r="C217" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -7030,16 +6421,16 @@
         <v>3</v>
       </c>
       <c r="F217" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="G217" t="s">
-        <v>207</v>
+        <v>15</v>
       </c>
       <c r="H217" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I217" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="218">
@@ -7050,7 +6441,7 @@
         <v>2016</v>
       </c>
       <c r="C218" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -7059,16 +6450,16 @@
         <v>4</v>
       </c>
       <c r="F218" t="s">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="G218" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="H218" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I218" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="219">
@@ -7079,7 +6470,7 @@
         <v>2017</v>
       </c>
       <c r="C219" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D219">
         <v>1</v>
@@ -7088,16 +6479,16 @@
         <v>4</v>
       </c>
       <c r="F219" t="s">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="G219" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="H219" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I219" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220">
@@ -7108,7 +6499,7 @@
         <v>2018</v>
       </c>
       <c r="C220" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D220">
         <v>1</v>
@@ -7117,16 +6508,16 @@
         <v>4</v>
       </c>
       <c r="F220" t="s">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="G220" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="H220" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I220" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="221">
@@ -7137,25 +6528,25 @@
         <v>2019</v>
       </c>
       <c r="C221" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F221" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="G221" t="s">
-        <v>208</v>
+        <v>15</v>
       </c>
       <c r="H221" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I221" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222">
@@ -7166,25 +6557,25 @@
         <v>2020</v>
       </c>
       <c r="C222" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E222">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F222" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="G222" t="s">
-        <v>208</v>
+        <v>15</v>
       </c>
       <c r="H222" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I222" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="223">
@@ -7195,7 +6586,7 @@
         <v>2021</v>
       </c>
       <c r="C223" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -7204,16 +6595,16 @@
         <v>3</v>
       </c>
       <c r="F223" t="s">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="G223" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="H223" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I223" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="224">
@@ -7224,7 +6615,7 @@
         <v>2022</v>
       </c>
       <c r="C224" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -7233,16 +6624,16 @@
         <v>3</v>
       </c>
       <c r="F224" t="s">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="G224" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="H224" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I224" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="225">
@@ -7253,7 +6644,7 @@
         <v>2023</v>
       </c>
       <c r="C225" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -7262,16 +6653,16 @@
         <v>3</v>
       </c>
       <c r="F225" t="s">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="G225" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="H225" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I225" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="226">
@@ -7282,25 +6673,25 @@
         <v>2024</v>
       </c>
       <c r="C226" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D226">
         <v>0</v>
       </c>
       <c r="E226">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F226" t="s">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="G226" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="H226" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I226" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="227">
@@ -7311,7 +6702,7 @@
         <v>2000</v>
       </c>
       <c r="C227" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -7320,16 +6711,16 @@
         <v>3</v>
       </c>
       <c r="F227" t="s">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="G227" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="H227" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I227" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="228">
@@ -7340,7 +6731,7 @@
         <v>2001</v>
       </c>
       <c r="C228" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D228">
         <v>1</v>
@@ -7349,16 +6740,16 @@
         <v>4</v>
       </c>
       <c r="F228" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="G228" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="H228" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I228" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="229">
@@ -7369,7 +6760,7 @@
         <v>2002</v>
       </c>
       <c r="C229" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -7378,16 +6769,16 @@
         <v>4</v>
       </c>
       <c r="F229" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="G229" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="H229" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I229" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="230">
@@ -7398,7 +6789,7 @@
         <v>2003</v>
       </c>
       <c r="C230" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -7407,16 +6798,16 @@
         <v>4</v>
       </c>
       <c r="F230" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="G230" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="H230" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I230" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="231">
@@ -7427,7 +6818,7 @@
         <v>2004</v>
       </c>
       <c r="C231" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D231">
         <v>1</v>
@@ -7436,16 +6827,16 @@
         <v>4</v>
       </c>
       <c r="F231" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="G231" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="H231" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I231" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="232">
@@ -7456,7 +6847,7 @@
         <v>2005</v>
       </c>
       <c r="C232" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -7465,16 +6856,16 @@
         <v>4</v>
       </c>
       <c r="F232" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="G232" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="H232" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I232" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="233">
@@ -7485,7 +6876,7 @@
         <v>2006</v>
       </c>
       <c r="C233" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D233">
         <v>1</v>
@@ -7494,16 +6885,16 @@
         <v>4</v>
       </c>
       <c r="F233" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="G233" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="H233" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I233" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234">
@@ -7514,7 +6905,7 @@
         <v>2007</v>
       </c>
       <c r="C234" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D234">
         <v>1</v>
@@ -7523,16 +6914,16 @@
         <v>4</v>
       </c>
       <c r="F234" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="G234" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="H234" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I234" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="235">
@@ -7543,7 +6934,7 @@
         <v>2008</v>
       </c>
       <c r="C235" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="D235">
         <v>0</v>
@@ -7552,16 +6943,16 @@
         <v>2</v>
       </c>
       <c r="F235" t="s">
-        <v>178</v>
+        <v>20</v>
       </c>
       <c r="G235" t="s">
-        <v>211</v>
+        <v>15</v>
       </c>
       <c r="H235" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I235" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="236">
@@ -7572,7 +6963,7 @@
         <v>2009</v>
       </c>
       <c r="C236" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -7581,16 +6972,16 @@
         <v>4</v>
       </c>
       <c r="F236" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="G236" t="s">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="H236" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I236" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="237">
@@ -7601,7 +6992,7 @@
         <v>2010</v>
       </c>
       <c r="C237" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="D237">
         <v>1</v>
@@ -7610,16 +7001,16 @@
         <v>4</v>
       </c>
       <c r="F237" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="G237" t="s">
-        <v>212</v>
+        <v>14</v>
       </c>
       <c r="H237" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I237" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="238">
@@ -7630,7 +7021,7 @@
         <v>2011</v>
       </c>
       <c r="C238" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D238">
         <v>0</v>
@@ -7639,16 +7030,16 @@
         <v>2</v>
       </c>
       <c r="F238" t="s">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="G238" t="s">
-        <v>213</v>
+        <v>15</v>
       </c>
       <c r="H238" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I238" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="239">
@@ -7659,7 +7050,7 @@
         <v>2012</v>
       </c>
       <c r="C239" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -7668,16 +7059,16 @@
         <v>4</v>
       </c>
       <c r="F239" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="G239" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="H239" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I239" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="240">
@@ -7688,7 +7079,7 @@
         <v>2013</v>
       </c>
       <c r="C240" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D240">
         <v>1</v>
@@ -7697,16 +7088,16 @@
         <v>4</v>
       </c>
       <c r="F240" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="G240" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="H240" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I240" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="241">
@@ -7717,7 +7108,7 @@
         <v>2014</v>
       </c>
       <c r="C241" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D241">
         <v>1</v>
@@ -7726,16 +7117,16 @@
         <v>4</v>
       </c>
       <c r="F241" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="G241" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="H241" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I241" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="242">
@@ -7746,7 +7137,7 @@
         <v>2015</v>
       </c>
       <c r="C242" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -7755,16 +7146,16 @@
         <v>4</v>
       </c>
       <c r="F242" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="G242" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="H242" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I242" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="243">
@@ -7775,7 +7166,7 @@
         <v>2016</v>
       </c>
       <c r="C243" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D243">
         <v>1</v>
@@ -7784,16 +7175,16 @@
         <v>4</v>
       </c>
       <c r="F243" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="G243" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="H243" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I243" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="244">
@@ -7804,7 +7195,7 @@
         <v>2017</v>
       </c>
       <c r="C244" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D244">
         <v>1</v>
@@ -7813,16 +7204,16 @@
         <v>4</v>
       </c>
       <c r="F244" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="G244" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="H244" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I244" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="245">
@@ -7833,7 +7224,7 @@
         <v>2018</v>
       </c>
       <c r="C245" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D245">
         <v>0</v>
@@ -7842,16 +7233,16 @@
         <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="G245" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H245" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I245" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246">
@@ -7862,7 +7253,7 @@
         <v>2019</v>
       </c>
       <c r="C246" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D246">
         <v>0</v>
@@ -7871,16 +7262,16 @@
         <v>3</v>
       </c>
       <c r="F246" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="G246" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H246" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I246" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247">
@@ -7891,7 +7282,7 @@
         <v>2020</v>
       </c>
       <c r="C247" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D247">
         <v>0</v>
@@ -7900,16 +7291,16 @@
         <v>3</v>
       </c>
       <c r="F247" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="G247" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H247" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I247" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="248">
@@ -7920,7 +7311,7 @@
         <v>2021</v>
       </c>
       <c r="C248" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -7929,16 +7320,16 @@
         <v>3</v>
       </c>
       <c r="F248" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="G248" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H248" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I248" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="249">
@@ -7949,7 +7340,7 @@
         <v>2022</v>
       </c>
       <c r="C249" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D249">
         <v>0</v>
@@ -7958,16 +7349,16 @@
         <v>3</v>
       </c>
       <c r="F249" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="G249" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H249" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I249" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="250">
@@ -7978,7 +7369,7 @@
         <v>2023</v>
       </c>
       <c r="C250" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D250">
         <v>0</v>
@@ -7987,16 +7378,16 @@
         <v>3</v>
       </c>
       <c r="F250" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="G250" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H250" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I250" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="251">
@@ -8007,25 +7398,25 @@
         <v>2024</v>
       </c>
       <c r="C251" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="D251">
         <v>0</v>
       </c>
       <c r="E251">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F251" t="s">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="G251" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H251" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I251" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252">
@@ -8036,7 +7427,7 @@
         <v>2000</v>
       </c>
       <c r="C252" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -8045,16 +7436,16 @@
         <v>3</v>
       </c>
       <c r="F252" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="G252" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H252" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I252" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="253">
@@ -8065,7 +7456,7 @@
         <v>2001</v>
       </c>
       <c r="C253" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D253">
         <v>0</v>
@@ -8074,16 +7465,16 @@
         <v>3</v>
       </c>
       <c r="F253" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="G253" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H253" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I253" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="254">
@@ -8094,7 +7485,7 @@
         <v>2002</v>
       </c>
       <c r="C254" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D254">
         <v>0</v>
@@ -8103,16 +7494,16 @@
         <v>3</v>
       </c>
       <c r="F254" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="G254" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H254" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I254" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="255">
@@ -8123,7 +7514,7 @@
         <v>2003</v>
       </c>
       <c r="C255" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D255">
         <v>0</v>
@@ -8132,16 +7523,16 @@
         <v>3</v>
       </c>
       <c r="F255" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="G255" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H255" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I255" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="256">
@@ -8152,7 +7543,7 @@
         <v>2004</v>
       </c>
       <c r="C256" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D256">
         <v>0</v>
@@ -8161,16 +7552,16 @@
         <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="G256" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H256" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I256" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257">
@@ -8181,7 +7572,7 @@
         <v>2005</v>
       </c>
       <c r="C257" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -8190,16 +7581,16 @@
         <v>3</v>
       </c>
       <c r="F257" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="G257" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H257" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I257" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="258">
@@ -8210,7 +7601,7 @@
         <v>2006</v>
       </c>
       <c r="C258" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="D258">
         <v>0</v>
@@ -8219,16 +7610,16 @@
         <v>2</v>
       </c>
       <c r="F258" t="s">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="G258" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H258" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I258" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="259">
@@ -8239,7 +7630,7 @@
         <v>2007</v>
       </c>
       <c r="C259" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D259">
         <v>0</v>
@@ -8248,16 +7639,16 @@
         <v>3</v>
       </c>
       <c r="F259" t="s">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="G259" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H259" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I259" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="260">
@@ -8268,7 +7659,7 @@
         <v>2008</v>
       </c>
       <c r="C260" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -8277,16 +7668,16 @@
         <v>3</v>
       </c>
       <c r="F260" t="s">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="G260" t="s">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="H260" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I260" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="261">
@@ -8297,7 +7688,7 @@
         <v>2009</v>
       </c>
       <c r="C261" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D261">
         <v>1</v>
@@ -8306,16 +7697,16 @@
         <v>5</v>
       </c>
       <c r="F261" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G261" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="H261" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I261" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="262">
@@ -8326,7 +7717,7 @@
         <v>2010</v>
       </c>
       <c r="C262" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D262">
         <v>1</v>
@@ -8335,16 +7726,16 @@
         <v>5</v>
       </c>
       <c r="F262" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G262" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="H262" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I262" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="263">
@@ -8355,7 +7746,7 @@
         <v>2011</v>
       </c>
       <c r="C263" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D263">
         <v>1</v>
@@ -8364,16 +7755,16 @@
         <v>5</v>
       </c>
       <c r="F263" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G263" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="H263" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I263" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="264">
@@ -8384,7 +7775,7 @@
         <v>2012</v>
       </c>
       <c r="C264" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -8393,16 +7784,16 @@
         <v>5</v>
       </c>
       <c r="F264" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G264" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="H264" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I264" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="265">
@@ -8413,7 +7804,7 @@
         <v>2013</v>
       </c>
       <c r="C265" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -8422,16 +7813,16 @@
         <v>5</v>
       </c>
       <c r="F265" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G265" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="H265" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I265" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="266">
@@ -8442,7 +7833,7 @@
         <v>2014</v>
       </c>
       <c r="C266" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D266">
         <v>1</v>
@@ -8451,16 +7842,16 @@
         <v>5</v>
       </c>
       <c r="F266" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G266" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="H266" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I266" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="267">
@@ -8471,7 +7862,7 @@
         <v>2015</v>
       </c>
       <c r="C267" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D267">
         <v>1</v>
@@ -8480,16 +7871,16 @@
         <v>5</v>
       </c>
       <c r="F267" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G267" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="H267" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I267" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="268">
@@ -8500,7 +7891,7 @@
         <v>2016</v>
       </c>
       <c r="C268" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -8509,16 +7900,16 @@
         <v>5</v>
       </c>
       <c r="F268" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="G268" t="s">
-        <v>216</v>
+        <v>14</v>
       </c>
       <c r="H268" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I268" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="269">
@@ -8529,7 +7920,7 @@
         <v>2017</v>
       </c>
       <c r="C269" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D269">
         <v>0</v>
@@ -8538,16 +7929,16 @@
         <v>3</v>
       </c>
       <c r="F269" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G269" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H269" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I269" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="270">
@@ -8558,7 +7949,7 @@
         <v>2018</v>
       </c>
       <c r="C270" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -8567,16 +7958,16 @@
         <v>3</v>
       </c>
       <c r="F270" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G270" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H270" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I270" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="271">
@@ -8587,7 +7978,7 @@
         <v>2019</v>
       </c>
       <c r="C271" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D271">
         <v>0</v>
@@ -8596,16 +7987,16 @@
         <v>3</v>
       </c>
       <c r="F271" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G271" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H271" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I271" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="272">
@@ -8616,7 +8007,7 @@
         <v>2020</v>
       </c>
       <c r="C272" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D272">
         <v>0</v>
@@ -8625,16 +8016,16 @@
         <v>3</v>
       </c>
       <c r="F272" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G272" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H272" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I272" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="273">
@@ -8645,7 +8036,7 @@
         <v>2021</v>
       </c>
       <c r="C273" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -8654,16 +8045,16 @@
         <v>3</v>
       </c>
       <c r="F273" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G273" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H273" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I273" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="274">
@@ -8674,7 +8065,7 @@
         <v>2022</v>
       </c>
       <c r="C274" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D274">
         <v>0</v>
@@ -8683,16 +8074,16 @@
         <v>3</v>
       </c>
       <c r="F274" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G274" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H274" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I274" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="275">
@@ -8703,7 +8094,7 @@
         <v>2023</v>
       </c>
       <c r="C275" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="D275">
         <v>0</v>
@@ -8712,16 +8103,16 @@
         <v>3</v>
       </c>
       <c r="F275" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G275" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H275" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I275" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276">
@@ -8732,25 +8123,25 @@
         <v>2024</v>
       </c>
       <c r="C276" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="D276">
         <v>0</v>
       </c>
       <c r="E276">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F276" t="s">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="G276" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H276" t="s">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="I276" t="s">
-        <v>229</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/data_reports/latam_availability.xlsx
+++ b/output/data_reports/latam_availability.xlsx
@@ -4762,16 +4762,16 @@
         <v>14</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F160" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H160" t="s">
         <v>15</v>
@@ -4791,16 +4791,16 @@
         <v>14</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F161" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H161" t="s">
         <v>15</v>
@@ -4820,16 +4820,16 @@
         <v>14</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F162" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H162" t="s">
         <v>15</v>
@@ -4849,16 +4849,16 @@
         <v>14</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F163" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H163" t="s">
         <v>15</v>
@@ -5528,7 +5528,7 @@
         <v>14</v>
       </c>
       <c r="H186" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I186" t="s">
         <v>15</v>
@@ -5557,7 +5557,7 @@
         <v>14</v>
       </c>
       <c r="H187" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I187" t="s">
         <v>15</v>
@@ -5586,7 +5586,7 @@
         <v>14</v>
       </c>
       <c r="H188" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I188" t="s">
         <v>15</v>
@@ -5615,7 +5615,7 @@
         <v>14</v>
       </c>
       <c r="H189" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I189" t="s">
         <v>15</v>
@@ -5644,7 +5644,7 @@
         <v>14</v>
       </c>
       <c r="H190" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I190" t="s">
         <v>15</v>
@@ -5673,7 +5673,7 @@
         <v>14</v>
       </c>
       <c r="H191" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I191" t="s">
         <v>15</v>

--- a/output/data_reports/latam_availability.xlsx
+++ b/output/data_reports/latam_availability.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="27">
   <si>
     <t>country</t>
   </si>
@@ -137,7 +137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I276"/>
+  <dimension ref="A1:I287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,16 +896,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -914,7 +914,7 @@
         <v>22</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -928,22 +928,22 @@
         <v>2</v>
       </c>
       <c r="B28">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -957,22 +957,22 @@
         <v>2</v>
       </c>
       <c r="B29">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -986,22 +986,22 @@
         <v>2</v>
       </c>
       <c r="B30">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -1015,7 +1015,7 @@
         <v>2</v>
       </c>
       <c r="B31">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -1044,7 +1044,7 @@
         <v>2</v>
       </c>
       <c r="B32">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -1073,22 +1073,22 @@
         <v>2</v>
       </c>
       <c r="B33">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -1102,7 +1102,7 @@
         <v>2</v>
       </c>
       <c r="B34">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
@@ -1131,7 +1131,7 @@
         <v>2</v>
       </c>
       <c r="B35">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -1160,7 +1160,7 @@
         <v>2</v>
       </c>
       <c r="B36">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -1189,19 +1189,19 @@
         <v>2</v>
       </c>
       <c r="B37">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37" t="s">
         <v>14</v>
@@ -1218,19 +1218,19 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
         <v>14</v>
@@ -1247,7 +1247,7 @@
         <v>2</v>
       </c>
       <c r="B39">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -1276,7 +1276,7 @@
         <v>2</v>
       </c>
       <c r="B40">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -1305,7 +1305,7 @@
         <v>2</v>
       </c>
       <c r="B41">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -1334,7 +1334,7 @@
         <v>2</v>
       </c>
       <c r="B42">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -1363,7 +1363,7 @@
         <v>2</v>
       </c>
       <c r="B43">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
@@ -1392,7 +1392,7 @@
         <v>2</v>
       </c>
       <c r="B44">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -1421,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="B45">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -1450,7 +1450,7 @@
         <v>2</v>
       </c>
       <c r="B46">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="B47">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -1508,7 +1508,7 @@
         <v>2</v>
       </c>
       <c r="B48">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -1537,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="B49">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
@@ -1566,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="B50">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -1595,7 +1595,7 @@
         <v>2</v>
       </c>
       <c r="B51">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -1621,25 +1621,25 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52">
-        <v>2000</v>
+        <v>2024</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53">
-        <v>2001</v>
+        <v>2025</v>
       </c>
       <c r="C53" t="s">
         <v>15</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
@@ -1682,19 +1682,19 @@
         <v>3</v>
       </c>
       <c r="B54">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
@@ -1711,19 +1711,19 @@
         <v>3</v>
       </c>
       <c r="B55">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
@@ -1740,7 +1740,7 @@
         <v>3</v>
       </c>
       <c r="B56">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C56" t="s">
         <v>15</v>
@@ -1769,22 +1769,22 @@
         <v>3</v>
       </c>
       <c r="B57">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -1798,22 +1798,22 @@
         <v>3</v>
       </c>
       <c r="B58">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -1827,7 +1827,7 @@
         <v>3</v>
       </c>
       <c r="B59">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C59" t="s">
         <v>15</v>
@@ -1856,19 +1856,19 @@
         <v>3</v>
       </c>
       <c r="B60">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D60">
         <v>1</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G60" t="s">
         <v>14</v>
@@ -1885,19 +1885,19 @@
         <v>3</v>
       </c>
       <c r="B61">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D61">
         <v>1</v>
       </c>
       <c r="E61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G61" t="s">
         <v>14</v>
@@ -1914,7 +1914,7 @@
         <v>3</v>
       </c>
       <c r="B62">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C62" t="s">
         <v>15</v>
@@ -1943,7 +1943,7 @@
         <v>3</v>
       </c>
       <c r="B63">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -1972,13 +1972,13 @@
         <v>3</v>
       </c>
       <c r="B64">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C64" t="s">
         <v>15</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -1987,7 +1987,7 @@
         <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -2001,7 +2001,7 @@
         <v>3</v>
       </c>
       <c r="B65">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -2030,13 +2030,13 @@
         <v>3</v>
       </c>
       <c r="B66">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66">
         <v>2</v>
@@ -2045,7 +2045,7 @@
         <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -2059,7 +2059,7 @@
         <v>3</v>
       </c>
       <c r="B67">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -2088,7 +2088,7 @@
         <v>3</v>
       </c>
       <c r="B68">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C68" t="s">
         <v>15</v>
@@ -2117,7 +2117,7 @@
         <v>3</v>
       </c>
       <c r="B69">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -2146,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="B70">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
@@ -2175,19 +2175,19 @@
         <v>3</v>
       </c>
       <c r="B71">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G71" t="s">
         <v>14</v>
@@ -2204,19 +2204,19 @@
         <v>3</v>
       </c>
       <c r="B72">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D72">
         <v>1</v>
       </c>
       <c r="E72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G72" t="s">
         <v>14</v>
@@ -2233,7 +2233,7 @@
         <v>3</v>
       </c>
       <c r="B73">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C73" t="s">
         <v>15</v>
@@ -2262,7 +2262,7 @@
         <v>3</v>
       </c>
       <c r="B74">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -2291,7 +2291,7 @@
         <v>3</v>
       </c>
       <c r="B75">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C75" t="s">
         <v>15</v>
@@ -2320,7 +2320,7 @@
         <v>3</v>
       </c>
       <c r="B76">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -2346,25 +2346,25 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B77">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="C77" t="s">
         <v>15</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -2375,25 +2375,25 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B78">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F78" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -2404,22 +2404,22 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B79">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
@@ -2436,19 +2436,19 @@
         <v>4</v>
       </c>
       <c r="B80">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
@@ -2465,19 +2465,19 @@
         <v>4</v>
       </c>
       <c r="B81">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
@@ -2494,7 +2494,7 @@
         <v>4</v>
       </c>
       <c r="B82">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -2523,19 +2523,19 @@
         <v>4</v>
       </c>
       <c r="B83">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
       <c r="E83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
@@ -2552,19 +2552,19 @@
         <v>4</v>
       </c>
       <c r="B84">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
@@ -2581,7 +2581,7 @@
         <v>4</v>
       </c>
       <c r="B85">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -2610,19 +2610,19 @@
         <v>4</v>
       </c>
       <c r="B86">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G86" t="s">
         <v>15</v>
@@ -2639,19 +2639,19 @@
         <v>4</v>
       </c>
       <c r="B87">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
       <c r="E87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
@@ -2668,7 +2668,7 @@
         <v>4</v>
       </c>
       <c r="B88">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -2697,7 +2697,7 @@
         <v>4</v>
       </c>
       <c r="B89">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -2726,7 +2726,7 @@
         <v>4</v>
       </c>
       <c r="B90">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -2755,22 +2755,22 @@
         <v>4</v>
       </c>
       <c r="B91">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -2784,22 +2784,22 @@
         <v>4</v>
       </c>
       <c r="B92">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -2813,22 +2813,22 @@
         <v>4</v>
       </c>
       <c r="B93">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G93" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -2842,7 +2842,7 @@
         <v>4</v>
       </c>
       <c r="B94">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
@@ -2871,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="B95">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
@@ -2900,7 +2900,7 @@
         <v>4</v>
       </c>
       <c r="B96">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -2929,7 +2929,7 @@
         <v>4</v>
       </c>
       <c r="B97">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -2958,7 +2958,7 @@
         <v>4</v>
       </c>
       <c r="B98">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C98" t="s">
         <v>14</v>
@@ -2987,7 +2987,7 @@
         <v>4</v>
       </c>
       <c r="B99">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C99" t="s">
         <v>14</v>
@@ -3016,7 +3016,7 @@
         <v>4</v>
       </c>
       <c r="B100">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -3045,22 +3045,22 @@
         <v>4</v>
       </c>
       <c r="B101">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -3071,25 +3071,25 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B102">
-        <v>2000</v>
+        <v>2022</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B103">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
@@ -3112,16 +3112,16 @@
         <v>1</v>
       </c>
       <c r="E103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F103" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H103" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
@@ -3129,28 +3129,28 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B104">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I104" t="s">
         <v>15</v>
@@ -3158,28 +3158,28 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B105">
-        <v>2003</v>
+        <v>2025</v>
       </c>
       <c r="C105" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I105" t="s">
         <v>15</v>
@@ -3190,25 +3190,25 @@
         <v>5</v>
       </c>
       <c r="B106">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
       </c>
       <c r="H106" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I106" t="s">
         <v>15</v>
@@ -3219,7 +3219,7 @@
         <v>5</v>
       </c>
       <c r="B107">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
@@ -3248,7 +3248,7 @@
         <v>5</v>
       </c>
       <c r="B108">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
@@ -3277,7 +3277,7 @@
         <v>5</v>
       </c>
       <c r="B109">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
@@ -3306,7 +3306,7 @@
         <v>5</v>
       </c>
       <c r="B110">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="C110" t="s">
         <v>14</v>
@@ -3335,7 +3335,7 @@
         <v>5</v>
       </c>
       <c r="B111">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
@@ -3364,7 +3364,7 @@
         <v>5</v>
       </c>
       <c r="B112">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C112" t="s">
         <v>14</v>
@@ -3385,7 +3385,7 @@
         <v>14</v>
       </c>
       <c r="I112" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113">
@@ -3393,7 +3393,7 @@
         <v>5</v>
       </c>
       <c r="B113">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
@@ -3414,7 +3414,7 @@
         <v>14</v>
       </c>
       <c r="I113" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114">
@@ -3422,7 +3422,7 @@
         <v>5</v>
       </c>
       <c r="B114">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C114" t="s">
         <v>14</v>
@@ -3443,7 +3443,7 @@
         <v>14</v>
       </c>
       <c r="I114" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115">
@@ -3451,7 +3451,7 @@
         <v>5</v>
       </c>
       <c r="B115">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
@@ -3472,7 +3472,7 @@
         <v>14</v>
       </c>
       <c r="I115" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116">
@@ -3480,7 +3480,7 @@
         <v>5</v>
       </c>
       <c r="B116">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
@@ -3509,7 +3509,7 @@
         <v>5</v>
       </c>
       <c r="B117">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="C117" t="s">
         <v>14</v>
@@ -3538,7 +3538,7 @@
         <v>5</v>
       </c>
       <c r="B118">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C118" t="s">
         <v>14</v>
@@ -3567,28 +3567,28 @@
         <v>5</v>
       </c>
       <c r="B119">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C119" t="s">
         <v>14</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F119" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G119" t="s">
         <v>15</v>
       </c>
       <c r="H119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
@@ -3596,28 +3596,28 @@
         <v>5</v>
       </c>
       <c r="B120">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C120" t="s">
         <v>14</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F120" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
@@ -3625,28 +3625,28 @@
         <v>5</v>
       </c>
       <c r="B121">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C121" t="s">
         <v>14</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F121" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G121" t="s">
         <v>15</v>
       </c>
       <c r="H121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122">
@@ -3654,28 +3654,28 @@
         <v>5</v>
       </c>
       <c r="B122">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F122" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G122" t="s">
         <v>15</v>
       </c>
       <c r="H122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123">
@@ -3683,7 +3683,7 @@
         <v>5</v>
       </c>
       <c r="B123">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C123" t="s">
         <v>14</v>
@@ -3712,7 +3712,7 @@
         <v>5</v>
       </c>
       <c r="B124">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C124" t="s">
         <v>14</v>
@@ -3741,7 +3741,7 @@
         <v>5</v>
       </c>
       <c r="B125">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="C125" t="s">
         <v>14</v>
@@ -3770,7 +3770,7 @@
         <v>5</v>
       </c>
       <c r="B126">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B127">
-        <v>2000</v>
+        <v>2021</v>
       </c>
       <c r="C127" t="s">
         <v>14</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B128">
-        <v>2001</v>
+        <v>2022</v>
       </c>
       <c r="C128" t="s">
         <v>14</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B129">
-        <v>2002</v>
+        <v>2023</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
@@ -3883,10 +3883,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B130">
-        <v>2003</v>
+        <v>2024</v>
       </c>
       <c r="C130" t="s">
         <v>14</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B131">
-        <v>2004</v>
+        <v>2025</v>
       </c>
       <c r="C131" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G131" t="s">
         <v>15</v>
@@ -3944,7 +3944,7 @@
         <v>6</v>
       </c>
       <c r="B132">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="C132" t="s">
         <v>14</v>
@@ -3973,7 +3973,7 @@
         <v>6</v>
       </c>
       <c r="B133">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
@@ -4002,7 +4002,7 @@
         <v>6</v>
       </c>
       <c r="B134">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="C134" t="s">
         <v>14</v>
@@ -4031,7 +4031,7 @@
         <v>6</v>
       </c>
       <c r="B135">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="C135" t="s">
         <v>14</v>
@@ -4060,7 +4060,7 @@
         <v>6</v>
       </c>
       <c r="B136">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
@@ -4089,7 +4089,7 @@
         <v>6</v>
       </c>
       <c r="B137">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
@@ -4118,7 +4118,7 @@
         <v>6</v>
       </c>
       <c r="B138">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
@@ -4147,22 +4147,22 @@
         <v>6</v>
       </c>
       <c r="B139">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F139" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G139" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H139" t="s">
         <v>15</v>
@@ -4176,22 +4176,22 @@
         <v>6</v>
       </c>
       <c r="B140">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="C140" t="s">
         <v>14</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F140" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H140" t="s">
         <v>15</v>
@@ -4205,22 +4205,22 @@
         <v>6</v>
       </c>
       <c r="B141">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
       </c>
       <c r="D141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F141" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G141" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H141" t="s">
         <v>15</v>
@@ -4234,22 +4234,22 @@
         <v>6</v>
       </c>
       <c r="B142">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="C142" t="s">
         <v>14</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G142" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H142" t="s">
         <v>15</v>
@@ -4263,22 +4263,22 @@
         <v>6</v>
       </c>
       <c r="B143">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="C143" t="s">
         <v>14</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F143" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G143" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H143" t="s">
         <v>15</v>
@@ -4292,7 +4292,7 @@
         <v>6</v>
       </c>
       <c r="B144">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C144" t="s">
         <v>14</v>
@@ -4321,7 +4321,7 @@
         <v>6</v>
       </c>
       <c r="B145">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C145" t="s">
         <v>14</v>
@@ -4350,7 +4350,7 @@
         <v>6</v>
       </c>
       <c r="B146">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C146" t="s">
         <v>14</v>
@@ -4379,7 +4379,7 @@
         <v>6</v>
       </c>
       <c r="B147">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
@@ -4408,22 +4408,22 @@
         <v>6</v>
       </c>
       <c r="B148">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F148" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H148" t="s">
         <v>15</v>
@@ -4437,22 +4437,22 @@
         <v>6</v>
       </c>
       <c r="B149">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F149" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H149" t="s">
         <v>15</v>
@@ -4466,22 +4466,22 @@
         <v>6</v>
       </c>
       <c r="B150">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H150" t="s">
         <v>15</v>
@@ -4495,22 +4495,22 @@
         <v>6</v>
       </c>
       <c r="B151">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="C151" t="s">
         <v>14</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F151" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H151" t="s">
         <v>15</v>
@@ -4521,25 +4521,25 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B152">
-        <v>2000</v>
+        <v>2020</v>
       </c>
       <c r="C152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F152" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H152" t="s">
         <v>15</v>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B153">
-        <v>2001</v>
+        <v>2021</v>
       </c>
       <c r="C153" t="s">
         <v>14</v>
@@ -4579,22 +4579,22 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B154">
-        <v>2002</v>
+        <v>2022</v>
       </c>
       <c r="C154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G154" t="s">
         <v>15</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B155">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="C155" t="s">
         <v>14</v>
@@ -4637,22 +4637,22 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B156">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="C156" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F156" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G156" t="s">
         <v>15</v>
@@ -4666,22 +4666,22 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B157">
-        <v>2005</v>
+        <v>2025</v>
       </c>
       <c r="C157" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G157" t="s">
         <v>15</v>
@@ -4698,19 +4698,19 @@
         <v>7</v>
       </c>
       <c r="B158">
-        <v>2006</v>
+        <v>2000</v>
       </c>
       <c r="C158" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
@@ -4727,7 +4727,7 @@
         <v>7</v>
       </c>
       <c r="B159">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="C159" t="s">
         <v>14</v>
@@ -4756,22 +4756,22 @@
         <v>7</v>
       </c>
       <c r="B160">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="C160" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G160" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H160" t="s">
         <v>15</v>
@@ -4785,22 +4785,22 @@
         <v>7</v>
       </c>
       <c r="B161">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="C161" t="s">
         <v>14</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F161" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G161" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H161" t="s">
         <v>15</v>
@@ -4814,22 +4814,22 @@
         <v>7</v>
       </c>
       <c r="B162">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="C162" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F162" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G162" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H162" t="s">
         <v>15</v>
@@ -4843,22 +4843,22 @@
         <v>7</v>
       </c>
       <c r="B163">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="C163" t="s">
         <v>14</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F163" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G163" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H163" t="s">
         <v>15</v>
@@ -4872,7 +4872,7 @@
         <v>7</v>
       </c>
       <c r="B164">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="C164" t="s">
         <v>14</v>
@@ -4901,7 +4901,7 @@
         <v>7</v>
       </c>
       <c r="B165">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="C165" t="s">
         <v>14</v>
@@ -4930,22 +4930,22 @@
         <v>7</v>
       </c>
       <c r="B166">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C166" t="s">
         <v>14</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F166" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H166" t="s">
         <v>15</v>
@@ -4959,22 +4959,22 @@
         <v>7</v>
       </c>
       <c r="B167">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C167" t="s">
         <v>14</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F167" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H167" t="s">
         <v>15</v>
@@ -4988,22 +4988,22 @@
         <v>7</v>
       </c>
       <c r="B168">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C168" t="s">
         <v>14</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F168" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H168" t="s">
         <v>15</v>
@@ -5017,22 +5017,22 @@
         <v>7</v>
       </c>
       <c r="B169">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C169" t="s">
         <v>14</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F169" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H169" t="s">
         <v>15</v>
@@ -5046,7 +5046,7 @@
         <v>7</v>
       </c>
       <c r="B170">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C170" t="s">
         <v>14</v>
@@ -5075,7 +5075,7 @@
         <v>7</v>
       </c>
       <c r="B171">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C171" t="s">
         <v>14</v>
@@ -5104,7 +5104,7 @@
         <v>7</v>
       </c>
       <c r="B172">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C172" t="s">
         <v>14</v>
@@ -5133,7 +5133,7 @@
         <v>7</v>
       </c>
       <c r="B173">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C173" t="s">
         <v>14</v>
@@ -5162,7 +5162,7 @@
         <v>7</v>
       </c>
       <c r="B174">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C174" t="s">
         <v>14</v>
@@ -5191,7 +5191,7 @@
         <v>7</v>
       </c>
       <c r="B175">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="C175" t="s">
         <v>14</v>
@@ -5220,7 +5220,7 @@
         <v>7</v>
       </c>
       <c r="B176">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="C176" t="s">
         <v>14</v>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B177">
-        <v>2000</v>
+        <v>2019</v>
       </c>
       <c r="C177" t="s">
         <v>14</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B178">
-        <v>2001</v>
+        <v>2020</v>
       </c>
       <c r="C178" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D178">
         <v>0</v>
       </c>
       <c r="E178">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F178" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G178" t="s">
         <v>15</v>
@@ -5304,10 +5304,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B179">
-        <v>2002</v>
+        <v>2021</v>
       </c>
       <c r="C179" t="s">
         <v>14</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B180">
-        <v>2003</v>
+        <v>2022</v>
       </c>
       <c r="C180" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D180">
         <v>0</v>
       </c>
       <c r="E180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F180" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G180" t="s">
         <v>15</v>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B181">
-        <v>2004</v>
+        <v>2023</v>
       </c>
       <c r="C181" t="s">
         <v>14</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B182">
-        <v>2005</v>
+        <v>2024</v>
       </c>
       <c r="C182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D182">
         <v>0</v>
       </c>
       <c r="E182">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G182" t="s">
         <v>15</v>
@@ -5420,22 +5420,22 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B183">
-        <v>2006</v>
+        <v>2025</v>
       </c>
       <c r="C183" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D183">
         <v>0</v>
       </c>
       <c r="E183">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F183" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G183" t="s">
         <v>15</v>
@@ -5452,19 +5452,19 @@
         <v>8</v>
       </c>
       <c r="B184">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="C184" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D184">
         <v>0</v>
       </c>
       <c r="E184">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F184" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
@@ -5481,19 +5481,19 @@
         <v>8</v>
       </c>
       <c r="B185">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="C185" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D185">
         <v>0</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F185" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G185" t="s">
         <v>15</v>
@@ -5510,25 +5510,25 @@
         <v>8</v>
       </c>
       <c r="B186">
-        <v>2009</v>
+        <v>2002</v>
       </c>
       <c r="C186" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F186" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G186" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H186" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I186" t="s">
         <v>15</v>
@@ -5539,25 +5539,25 @@
         <v>8</v>
       </c>
       <c r="B187">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="C187" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F187" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G187" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H187" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I187" t="s">
         <v>15</v>
@@ -5568,25 +5568,25 @@
         <v>8</v>
       </c>
       <c r="B188">
-        <v>2011</v>
+        <v>2004</v>
       </c>
       <c r="C188" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F188" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G188" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H188" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I188" t="s">
         <v>15</v>
@@ -5597,25 +5597,25 @@
         <v>8</v>
       </c>
       <c r="B189">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="C189" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E189">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F189" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G189" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H189" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I189" t="s">
         <v>15</v>
@@ -5626,25 +5626,25 @@
         <v>8</v>
       </c>
       <c r="B190">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="C190" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F190" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G190" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H190" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I190" t="s">
         <v>15</v>
@@ -5655,25 +5655,25 @@
         <v>8</v>
       </c>
       <c r="B191">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="C191" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F191" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G191" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H191" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I191" t="s">
         <v>15</v>
@@ -5684,19 +5684,19 @@
         <v>8</v>
       </c>
       <c r="B192">
-        <v>2015</v>
+        <v>2008</v>
       </c>
       <c r="C192" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D192">
         <v>0</v>
       </c>
       <c r="E192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F192" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G192" t="s">
         <v>15</v>
@@ -5713,25 +5713,25 @@
         <v>8</v>
       </c>
       <c r="B193">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="C193" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F193" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G193" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H193" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I193" t="s">
         <v>15</v>
@@ -5742,25 +5742,25 @@
         <v>8</v>
       </c>
       <c r="B194">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C194" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F194" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G194" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H194" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I194" t="s">
         <v>15</v>
@@ -5771,25 +5771,25 @@
         <v>8</v>
       </c>
       <c r="B195">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C195" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E195">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F195" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G195" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H195" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I195" t="s">
         <v>15</v>
@@ -5800,25 +5800,25 @@
         <v>8</v>
       </c>
       <c r="B196">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E196">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F196" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I196" t="s">
         <v>15</v>
@@ -5829,25 +5829,25 @@
         <v>8</v>
       </c>
       <c r="B197">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C197" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F197" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G197" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H197" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I197" t="s">
         <v>15</v>
@@ -5858,25 +5858,25 @@
         <v>8</v>
       </c>
       <c r="B198">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C198" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F198" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G198" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H198" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I198" t="s">
         <v>15</v>
@@ -5887,19 +5887,19 @@
         <v>8</v>
       </c>
       <c r="B199">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C199" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D199">
         <v>0</v>
       </c>
       <c r="E199">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F199" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G199" t="s">
         <v>15</v>
@@ -5916,19 +5916,19 @@
         <v>8</v>
       </c>
       <c r="B200">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="C200" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D200">
         <v>0</v>
       </c>
       <c r="E200">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F200" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G200" t="s">
         <v>15</v>
@@ -5945,19 +5945,19 @@
         <v>8</v>
       </c>
       <c r="B201">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="C201" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D201">
         <v>0</v>
       </c>
       <c r="E201">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F201" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G201" t="s">
         <v>15</v>
@@ -5971,10 +5971,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B202">
-        <v>2000</v>
+        <v>2018</v>
       </c>
       <c r="C202" t="s">
         <v>14</v>
@@ -6000,22 +6000,22 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B203">
-        <v>2001</v>
+        <v>2019</v>
       </c>
       <c r="C203" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D203">
         <v>0</v>
       </c>
       <c r="E203">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F203" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G203" t="s">
         <v>15</v>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B204">
-        <v>2002</v>
+        <v>2020</v>
       </c>
       <c r="C204" t="s">
         <v>14</v>
@@ -6058,22 +6058,22 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B205">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="C205" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D205">
         <v>0</v>
       </c>
       <c r="E205">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F205" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G205" t="s">
         <v>15</v>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B206">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="C206" t="s">
         <v>14</v>
@@ -6116,22 +6116,22 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B207">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="C207" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D207">
         <v>0</v>
       </c>
       <c r="E207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F207" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G207" t="s">
         <v>15</v>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B208">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="C208" t="s">
         <v>14</v>
@@ -6174,22 +6174,22 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B209">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="C209" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D209">
         <v>0</v>
       </c>
       <c r="E209">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G209" t="s">
         <v>15</v>
@@ -6206,7 +6206,7 @@
         <v>9</v>
       </c>
       <c r="B210">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="C210" t="s">
         <v>14</v>
@@ -6235,7 +6235,7 @@
         <v>9</v>
       </c>
       <c r="B211">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="C211" t="s">
         <v>14</v>
@@ -6264,7 +6264,7 @@
         <v>9</v>
       </c>
       <c r="B212">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="C212" t="s">
         <v>14</v>
@@ -6293,7 +6293,7 @@
         <v>9</v>
       </c>
       <c r="B213">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="C213" t="s">
         <v>14</v>
@@ -6322,7 +6322,7 @@
         <v>9</v>
       </c>
       <c r="B214">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="C214" t="s">
         <v>14</v>
@@ -6351,7 +6351,7 @@
         <v>9</v>
       </c>
       <c r="B215">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="C215" t="s">
         <v>14</v>
@@ -6380,7 +6380,7 @@
         <v>9</v>
       </c>
       <c r="B216">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="C216" t="s">
         <v>14</v>
@@ -6409,7 +6409,7 @@
         <v>9</v>
       </c>
       <c r="B217">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="C217" t="s">
         <v>14</v>
@@ -6438,22 +6438,22 @@
         <v>9</v>
       </c>
       <c r="B218">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="C218" t="s">
         <v>14</v>
       </c>
       <c r="D218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F218" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G218" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H218" t="s">
         <v>15</v>
@@ -6467,22 +6467,22 @@
         <v>9</v>
       </c>
       <c r="B219">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="C219" t="s">
         <v>14</v>
       </c>
       <c r="D219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E219">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F219" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G219" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H219" t="s">
         <v>15</v>
@@ -6496,22 +6496,22 @@
         <v>9</v>
       </c>
       <c r="B220">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="C220" t="s">
         <v>14</v>
       </c>
       <c r="D220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F220" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G220" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H220" t="s">
         <v>15</v>
@@ -6525,7 +6525,7 @@
         <v>9</v>
       </c>
       <c r="B221">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C221" t="s">
         <v>14</v>
@@ -6554,7 +6554,7 @@
         <v>9</v>
       </c>
       <c r="B222">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C222" t="s">
         <v>14</v>
@@ -6583,7 +6583,7 @@
         <v>9</v>
       </c>
       <c r="B223">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C223" t="s">
         <v>14</v>
@@ -6612,7 +6612,7 @@
         <v>9</v>
       </c>
       <c r="B224">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C224" t="s">
         <v>14</v>
@@ -6641,7 +6641,7 @@
         <v>9</v>
       </c>
       <c r="B225">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="C225" t="s">
         <v>14</v>
@@ -6670,22 +6670,22 @@
         <v>9</v>
       </c>
       <c r="B226">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="C226" t="s">
         <v>14</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E226">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F226" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G226" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H226" t="s">
         <v>15</v>
@@ -6696,25 +6696,25 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B227">
-        <v>2000</v>
+        <v>2017</v>
       </c>
       <c r="C227" t="s">
         <v>14</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F227" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G227" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H227" t="s">
         <v>15</v>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B228">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="C228" t="s">
         <v>14</v>
@@ -6754,10 +6754,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B229">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="C229" t="s">
         <v>14</v>
@@ -6783,10 +6783,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B230">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="C230" t="s">
         <v>14</v>
@@ -6812,25 +6812,25 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B231">
-        <v>2004</v>
+        <v>2021</v>
       </c>
       <c r="C231" t="s">
         <v>14</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F231" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G231" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H231" t="s">
         <v>15</v>
@@ -6841,25 +6841,25 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B232">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="C232" t="s">
         <v>14</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E232">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F232" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G232" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H232" t="s">
         <v>15</v>
@@ -6870,25 +6870,25 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B233">
-        <v>2006</v>
+        <v>2023</v>
       </c>
       <c r="C233" t="s">
         <v>14</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F233" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G233" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H233" t="s">
         <v>15</v>
@@ -6899,25 +6899,25 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B234">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="C234" t="s">
         <v>14</v>
       </c>
       <c r="D234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F234" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G234" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H234" t="s">
         <v>15</v>
@@ -6928,10 +6928,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B235">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="C235" t="s">
         <v>15</v>
@@ -6940,10 +6940,10 @@
         <v>0</v>
       </c>
       <c r="E235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G235" t="s">
         <v>15</v>
@@ -6960,22 +6960,22 @@
         <v>10</v>
       </c>
       <c r="B236">
-        <v>2009</v>
+        <v>2000</v>
       </c>
       <c r="C236" t="s">
         <v>14</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E236">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F236" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G236" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H236" t="s">
         <v>15</v>
@@ -6989,7 +6989,7 @@
         <v>10</v>
       </c>
       <c r="B237">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="C237" t="s">
         <v>14</v>
@@ -7018,22 +7018,22 @@
         <v>10</v>
       </c>
       <c r="B238">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="C238" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E238">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F238" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G238" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H238" t="s">
         <v>15</v>
@@ -7047,7 +7047,7 @@
         <v>10</v>
       </c>
       <c r="B239">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="C239" t="s">
         <v>14</v>
@@ -7076,7 +7076,7 @@
         <v>10</v>
       </c>
       <c r="B240">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="C240" t="s">
         <v>14</v>
@@ -7105,7 +7105,7 @@
         <v>10</v>
       </c>
       <c r="B241">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="C241" t="s">
         <v>14</v>
@@ -7134,7 +7134,7 @@
         <v>10</v>
       </c>
       <c r="B242">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="C242" t="s">
         <v>14</v>
@@ -7163,7 +7163,7 @@
         <v>10</v>
       </c>
       <c r="B243">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="C243" t="s">
         <v>14</v>
@@ -7192,22 +7192,22 @@
         <v>10</v>
       </c>
       <c r="B244">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="C244" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E244">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F244" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G244" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H244" t="s">
         <v>15</v>
@@ -7221,22 +7221,22 @@
         <v>10</v>
       </c>
       <c r="B245">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="C245" t="s">
         <v>14</v>
       </c>
       <c r="D245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E245">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F245" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G245" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H245" t="s">
         <v>15</v>
@@ -7250,22 +7250,22 @@
         <v>10</v>
       </c>
       <c r="B246">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="C246" t="s">
         <v>14</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E246">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F246" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G246" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H246" t="s">
         <v>15</v>
@@ -7279,19 +7279,19 @@
         <v>10</v>
       </c>
       <c r="B247">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C247" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D247">
         <v>0</v>
       </c>
       <c r="E247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F247" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G247" t="s">
         <v>15</v>
@@ -7308,22 +7308,22 @@
         <v>10</v>
       </c>
       <c r="B248">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C248" t="s">
         <v>14</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E248">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F248" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G248" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H248" t="s">
         <v>15</v>
@@ -7337,22 +7337,22 @@
         <v>10</v>
       </c>
       <c r="B249">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C249" t="s">
         <v>14</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E249">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F249" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G249" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H249" t="s">
         <v>15</v>
@@ -7366,22 +7366,22 @@
         <v>10</v>
       </c>
       <c r="B250">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="C250" t="s">
         <v>14</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F250" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G250" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H250" t="s">
         <v>15</v>
@@ -7395,22 +7395,22 @@
         <v>10</v>
       </c>
       <c r="B251">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="C251" t="s">
         <v>14</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E251">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F251" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G251" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H251" t="s">
         <v>15</v>
@@ -7421,25 +7421,25 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B252">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="C252" t="s">
         <v>14</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E252">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F252" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G252" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H252" t="s">
         <v>15</v>
@@ -7450,25 +7450,25 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B253">
-        <v>2001</v>
+        <v>2017</v>
       </c>
       <c r="C253" t="s">
         <v>14</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E253">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F253" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G253" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H253" t="s">
         <v>15</v>
@@ -7479,10 +7479,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B254">
-        <v>2002</v>
+        <v>2018</v>
       </c>
       <c r="C254" t="s">
         <v>14</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B255">
-        <v>2003</v>
+        <v>2019</v>
       </c>
       <c r="C255" t="s">
         <v>14</v>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B256">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="C256" t="s">
         <v>14</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B257">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="C257" t="s">
         <v>14</v>
@@ -7595,22 +7595,22 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B258">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C258" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D258">
         <v>0</v>
       </c>
       <c r="E258">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F258" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G258" t="s">
         <v>15</v>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B259">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="C259" t="s">
         <v>14</v>
@@ -7653,10 +7653,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B260">
-        <v>2008</v>
+        <v>2024</v>
       </c>
       <c r="C260" t="s">
         <v>14</v>
@@ -7682,25 +7682,25 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B261">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="C261" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E261">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F261" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G261" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H261" t="s">
         <v>15</v>
@@ -7714,22 +7714,22 @@
         <v>11</v>
       </c>
       <c r="B262">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="C262" t="s">
         <v>14</v>
       </c>
       <c r="D262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E262">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F262" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G262" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H262" t="s">
         <v>15</v>
@@ -7743,22 +7743,22 @@
         <v>11</v>
       </c>
       <c r="B263">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="C263" t="s">
         <v>14</v>
       </c>
       <c r="D263">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E263">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F263" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G263" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H263" t="s">
         <v>15</v>
@@ -7772,22 +7772,22 @@
         <v>11</v>
       </c>
       <c r="B264">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="C264" t="s">
         <v>14</v>
       </c>
       <c r="D264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E264">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F264" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G264" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H264" t="s">
         <v>15</v>
@@ -7801,22 +7801,22 @@
         <v>11</v>
       </c>
       <c r="B265">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="C265" t="s">
         <v>14</v>
       </c>
       <c r="D265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E265">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F265" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G265" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H265" t="s">
         <v>15</v>
@@ -7830,22 +7830,22 @@
         <v>11</v>
       </c>
       <c r="B266">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="C266" t="s">
         <v>14</v>
       </c>
       <c r="D266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E266">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F266" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G266" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H266" t="s">
         <v>15</v>
@@ -7859,22 +7859,22 @@
         <v>11</v>
       </c>
       <c r="B267">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="C267" t="s">
         <v>14</v>
       </c>
       <c r="D267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E267">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F267" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G267" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H267" t="s">
         <v>15</v>
@@ -7888,22 +7888,22 @@
         <v>11</v>
       </c>
       <c r="B268">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="C268" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E268">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F268" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G268" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H268" t="s">
         <v>15</v>
@@ -7917,7 +7917,7 @@
         <v>11</v>
       </c>
       <c r="B269">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="C269" t="s">
         <v>14</v>
@@ -7946,7 +7946,7 @@
         <v>11</v>
       </c>
       <c r="B270">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="C270" t="s">
         <v>14</v>
@@ -7975,22 +7975,22 @@
         <v>11</v>
       </c>
       <c r="B271">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="C271" t="s">
         <v>14</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E271">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F271" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G271" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H271" t="s">
         <v>15</v>
@@ -8004,22 +8004,22 @@
         <v>11</v>
       </c>
       <c r="B272">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C272" t="s">
         <v>14</v>
       </c>
       <c r="D272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E272">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F272" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G272" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H272" t="s">
         <v>15</v>
@@ -8033,22 +8033,22 @@
         <v>11</v>
       </c>
       <c r="B273">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C273" t="s">
         <v>14</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E273">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F273" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G273" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H273" t="s">
         <v>15</v>
@@ -8062,22 +8062,22 @@
         <v>11</v>
       </c>
       <c r="B274">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C274" t="s">
         <v>14</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E274">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F274" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G274" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H274" t="s">
         <v>15</v>
@@ -8091,22 +8091,22 @@
         <v>11</v>
       </c>
       <c r="B275">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="C275" t="s">
         <v>14</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E275">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F275" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G275" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H275" t="s">
         <v>15</v>
@@ -8120,27 +8120,346 @@
         <v>11</v>
       </c>
       <c r="B276">
+        <v>2014</v>
+      </c>
+      <c r="C276" t="s">
+        <v>14</v>
+      </c>
+      <c r="D276">
+        <v>1</v>
+      </c>
+      <c r="E276">
+        <v>5</v>
+      </c>
+      <c r="F276" t="s">
+        <v>23</v>
+      </c>
+      <c r="G276" t="s">
+        <v>14</v>
+      </c>
+      <c r="H276" t="s">
+        <v>15</v>
+      </c>
+      <c r="I276" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>11</v>
+      </c>
+      <c r="B277">
+        <v>2015</v>
+      </c>
+      <c r="C277" t="s">
+        <v>14</v>
+      </c>
+      <c r="D277">
+        <v>1</v>
+      </c>
+      <c r="E277">
+        <v>5</v>
+      </c>
+      <c r="F277" t="s">
+        <v>23</v>
+      </c>
+      <c r="G277" t="s">
+        <v>14</v>
+      </c>
+      <c r="H277" t="s">
+        <v>15</v>
+      </c>
+      <c r="I277" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>11</v>
+      </c>
+      <c r="B278">
+        <v>2016</v>
+      </c>
+      <c r="C278" t="s">
+        <v>14</v>
+      </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
+      <c r="E278">
+        <v>5</v>
+      </c>
+      <c r="F278" t="s">
+        <v>23</v>
+      </c>
+      <c r="G278" t="s">
+        <v>14</v>
+      </c>
+      <c r="H278" t="s">
+        <v>15</v>
+      </c>
+      <c r="I278" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>11</v>
+      </c>
+      <c r="B279">
+        <v>2017</v>
+      </c>
+      <c r="C279" t="s">
+        <v>14</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>3</v>
+      </c>
+      <c r="F279" t="s">
+        <v>21</v>
+      </c>
+      <c r="G279" t="s">
+        <v>15</v>
+      </c>
+      <c r="H279" t="s">
+        <v>15</v>
+      </c>
+      <c r="I279" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>11</v>
+      </c>
+      <c r="B280">
+        <v>2018</v>
+      </c>
+      <c r="C280" t="s">
+        <v>14</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>3</v>
+      </c>
+      <c r="F280" t="s">
+        <v>21</v>
+      </c>
+      <c r="G280" t="s">
+        <v>15</v>
+      </c>
+      <c r="H280" t="s">
+        <v>15</v>
+      </c>
+      <c r="I280" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>11</v>
+      </c>
+      <c r="B281">
+        <v>2019</v>
+      </c>
+      <c r="C281" t="s">
+        <v>14</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>3</v>
+      </c>
+      <c r="F281" t="s">
+        <v>21</v>
+      </c>
+      <c r="G281" t="s">
+        <v>15</v>
+      </c>
+      <c r="H281" t="s">
+        <v>15</v>
+      </c>
+      <c r="I281" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>11</v>
+      </c>
+      <c r="B282">
+        <v>2020</v>
+      </c>
+      <c r="C282" t="s">
+        <v>14</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>3</v>
+      </c>
+      <c r="F282" t="s">
+        <v>21</v>
+      </c>
+      <c r="G282" t="s">
+        <v>15</v>
+      </c>
+      <c r="H282" t="s">
+        <v>15</v>
+      </c>
+      <c r="I282" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>11</v>
+      </c>
+      <c r="B283">
+        <v>2021</v>
+      </c>
+      <c r="C283" t="s">
+        <v>14</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>3</v>
+      </c>
+      <c r="F283" t="s">
+        <v>21</v>
+      </c>
+      <c r="G283" t="s">
+        <v>15</v>
+      </c>
+      <c r="H283" t="s">
+        <v>15</v>
+      </c>
+      <c r="I283" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>11</v>
+      </c>
+      <c r="B284">
+        <v>2022</v>
+      </c>
+      <c r="C284" t="s">
+        <v>14</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>3</v>
+      </c>
+      <c r="F284" t="s">
+        <v>21</v>
+      </c>
+      <c r="G284" t="s">
+        <v>15</v>
+      </c>
+      <c r="H284" t="s">
+        <v>15</v>
+      </c>
+      <c r="I284" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>11</v>
+      </c>
+      <c r="B285">
+        <v>2023</v>
+      </c>
+      <c r="C285" t="s">
+        <v>14</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>3</v>
+      </c>
+      <c r="F285" t="s">
+        <v>21</v>
+      </c>
+      <c r="G285" t="s">
+        <v>15</v>
+      </c>
+      <c r="H285" t="s">
+        <v>15</v>
+      </c>
+      <c r="I285" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>11</v>
+      </c>
+      <c r="B286">
         <v>2024</v>
       </c>
-      <c r="C276" t="s">
-        <v>14</v>
-      </c>
-      <c r="D276">
-        <v>0</v>
-      </c>
-      <c r="E276">
-        <v>3</v>
-      </c>
-      <c r="F276" t="s">
-        <v>21</v>
-      </c>
-      <c r="G276" t="s">
-        <v>15</v>
-      </c>
-      <c r="H276" t="s">
-        <v>15</v>
-      </c>
-      <c r="I276" t="s">
+      <c r="C286" t="s">
+        <v>14</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>3</v>
+      </c>
+      <c r="F286" t="s">
+        <v>21</v>
+      </c>
+      <c r="G286" t="s">
+        <v>15</v>
+      </c>
+      <c r="H286" t="s">
+        <v>15</v>
+      </c>
+      <c r="I286" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>11</v>
+      </c>
+      <c r="B287">
+        <v>2025</v>
+      </c>
+      <c r="C287" t="s">
+        <v>15</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>1</v>
+      </c>
+      <c r="F287" t="s">
+        <v>22</v>
+      </c>
+      <c r="G287" t="s">
+        <v>15</v>
+      </c>
+      <c r="H287" t="s">
+        <v>15</v>
+      </c>
+      <c r="I287" t="s">
         <v>15</v>
       </c>
     </row>
